--- a/data/export/2026-10-17-浦东35路.xlsx
+++ b/data/export/2026-10-17-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1492,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1603,1228 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-17-浦东35路.xlsx
+++ b/data/export/2026-10-17-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>114分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,33 +812,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -854,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -887,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,17 +931,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -931,13 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -998,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1072,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1148,7 +1172,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1159,7 +1183,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1244,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1294,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1355,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1405,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1466,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1516,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1577,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1627,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1688,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1714,7 +1738,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1799,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1849,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1910,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1960,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2021,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2071,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2132,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2182,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2243,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2293,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2354,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2380,7 +2404,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2465,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2491,7 +2515,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2576,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2602,7 +2626,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2687,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2713,7 +2737,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2721,22 +2745,22 @@
       <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2769,12 +2793,12 @@
       <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2788,7 +2812,7 @@
       <c r="T21" s="2" t="inlineStr"/>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
@@ -2824,7 +2848,1125 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>2/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>1/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-17-浦东35路.xlsx
+++ b/data/export/2026-10-17-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC31"/>
+  <dimension ref="A1:AC38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -446,10 +446,10 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,14 +946,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
           <t>127.0</t>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -989,32 +989,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1022,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1046,33 +1050,37 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1183,7 +1191,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1211,32 +1219,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1244,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1268,33 +1280,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1322,32 +1338,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1355,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1379,33 +1399,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1505,7 +1529,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1516,7 +1540,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1544,32 +1568,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -1577,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1601,17 +1629,17 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
@@ -1621,13 +1649,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1655,32 +1687,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1688,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1712,17 +1748,17 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -1732,13 +1768,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1838,7 +1878,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1849,7 +1889,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1877,12 +1917,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq37推进至seq54，推进17站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1910,7 +1950,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1918,10 +1958,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
-      <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq23映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±6分钟；反向位置浦建路锦绣路 ETA 10分钟参与校验</t>
+        </is>
+      </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -1960,7 +2016,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2071,7 +2127,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2188,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2182,7 +2238,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2266,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq39推进至seq50，推进11站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2243,7 +2299,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2251,10 +2307,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr"/>
-      <c r="S16" s="2" t="inlineStr"/>
-      <c r="T16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq39（站名待映射） ETA 4分钟参与校验</t>
+        </is>
+      </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
           <t>07:24</t>
@@ -2293,7 +2365,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2426,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2404,7 +2476,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2465,7 +2537,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2515,7 +2587,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2648,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2626,7 +2698,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2687,7 +2759,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2737,7 +2809,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2798,7 +2870,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2848,7 +2920,7 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2909,7 +2981,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2959,7 +3031,7 @@
       <c r="AB22" s="2" t="inlineStr"/>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3092,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3070,7 +3142,7 @@
       <c r="AB23" s="2" t="inlineStr"/>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3203,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3181,7 +3253,7 @@
       <c r="AB24" s="2" t="inlineStr"/>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3314,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3292,7 +3364,7 @@
       <c r="AB25" s="2" t="inlineStr"/>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3425,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3403,7 +3475,7 @@
       <c r="AB26" s="2" t="inlineStr"/>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3536,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3514,7 +3586,7 @@
       <c r="AB27" s="2" t="inlineStr"/>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3575,7 +3647,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3629,7 +3701,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3762,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3744,7 +3816,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -3805,7 +3877,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3855,7 +3927,7 @@
       <c r="AB30" s="2" t="inlineStr"/>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3863,22 +3935,22 @@
       <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -3916,7 +3988,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3960,13 +4032,806 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr"/>
-      <c r="AC31" s="2" t="inlineStr">
-        <is>
-          <t>—/27</t>
+      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A92076D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-17-浦东35路.xlsx
+++ b/data/export/2026-10-17-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC38"/>
+  <dimension ref="A1:AC48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1644,14 +1644,14 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
           <t>129.0</t>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1697,24 +1697,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1763,22 +1763,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -1806,32 +1806,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1839,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1863,17 +1867,17 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -1883,13 +1887,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1930,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq37推进至seq54，推进17站，达到≥2站确认条件</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq37推进至seq58，推进21站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1950,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2077,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2116,7 +2124,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2155,32 +2163,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2188,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2212,33 +2224,37 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2287,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq39推进至seq50，推进11站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq39推进至seq58，推进19站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2299,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2393,32 +2409,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2426,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2450,33 +2470,37 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -2504,32 +2528,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -2537,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2561,33 +2589,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -2615,32 +2647,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2648,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2672,33 +2708,37 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -2726,32 +2766,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -2759,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2783,33 +2827,37 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -2837,32 +2885,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -2870,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2894,33 +2946,37 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -2948,32 +3004,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2981,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3005,17 +3065,17 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -3025,13 +3085,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3059,32 +3123,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -3092,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3116,33 +3184,37 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3203,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3281,32 +3353,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -3314,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3338,17 +3414,17 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -3358,13 +3434,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -3425,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3536,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3647,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3701,7 +3781,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3842,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3877,7 +3957,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3988,7 +4068,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4042,7 +4122,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4183,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4214,7 +4294,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4329,7 +4409,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4444,7 +4524,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4555,7 +4635,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4670,7 +4750,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4728,22 +4808,22 @@
       <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -4776,12 +4856,12 @@
       <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4825,13 +4905,1163 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>9/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>15/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>16/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB38" s="2" t="inlineStr"/>
-      <c r="AC38" s="2" t="inlineStr">
+      <c r="AB42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr">
         <is>
           <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>12/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>14/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>13/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>17/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>18/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>10/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-17-浦东35路.xlsx
+++ b/data/export/2026-10-17-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC48"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,17 +1065,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1529,18 +1529,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1659,7 +1663,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1778,7 +1782,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1897,7 +1901,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2200,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2446,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2500,7 +2504,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2619,7 +2623,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2738,7 +2742,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2847,17 +2851,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2976,7 +2980,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3242,32 +3246,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3275,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3299,17 +3307,17 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3319,13 +3327,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3429,14 +3441,14 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
           <t>128.0</t>
@@ -3444,7 +3456,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -3472,32 +3484,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3505,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3529,17 +3545,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3549,13 +3565,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -3583,32 +3603,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3616,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3640,33 +3664,37 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -3694,32 +3722,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3727,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3751,37 +3783,37 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -3809,32 +3841,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3842,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3866,17 +3902,17 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
@@ -3886,17 +3922,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -3924,32 +3960,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -3957,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3981,33 +4021,37 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -4068,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4122,7 +4166,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4222,7 +4266,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4261,32 +4305,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4294,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4318,32 +4366,32 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4376,32 +4424,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4409,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4433,17 +4485,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4453,17 +4505,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -4491,32 +4543,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -4524,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4548,33 +4604,37 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB35" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -4602,32 +4662,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4635,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4659,17 +4723,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4679,17 +4743,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4781,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq50，推进12站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4750,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4758,10 +4822,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q37" s="2" t="inlineStr"/>
-      <c r="R37" s="2" t="inlineStr"/>
-      <c r="S37" s="2" t="inlineStr"/>
-      <c r="T37" s="2" t="inlineStr"/>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±3分钟；反向位置物理seq38（站名待映射） ETA 10分钟参与校验</t>
+        </is>
+      </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
           <t>09:38</t>
@@ -4861,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4915,7 +4995,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4976,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5030,7 +5110,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -5091,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5145,7 +5225,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -5206,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5321,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5432,7 +5512,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5486,7 +5566,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5627,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5601,7 +5681,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -5662,7 +5742,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5716,7 +5796,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -5744,32 +5824,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>8分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -5777,7 +5861,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5801,17 +5885,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5821,17 +5905,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -5892,7 +5976,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5946,7 +6030,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -6007,7 +6091,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6065,6 +6149,807 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>6/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>23/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>130.5</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>13/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>19/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr"/>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>124.5</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>10/28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-17-浦东35路.xlsx
+++ b/data/export/2026-10-17-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC55"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,22 +1648,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1772,17 +1772,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1891,17 +1891,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2128,18 +2128,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2248,17 +2252,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,7 +2378,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2450,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2494,17 +2498,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2608,7 +2612,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2688,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2732,17 +2736,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2926,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2980,7 +2984,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -3099,7 +3103,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3218,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -3337,7 +3341,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3456,7 +3460,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3694,7 +3698,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3932,7 +3936,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -3997,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4166,7 +4170,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4342,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4515,7 +4519,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4634,7 +4638,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4786,7 +4790,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq50，推进12站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq61，推进23站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4814,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4869,7 +4873,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4908,32 +4912,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -4941,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4965,37 +4973,37 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -5023,32 +5031,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5056,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5080,17 +5092,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5100,17 +5112,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -5138,32 +5150,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5171,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5195,17 +5211,17 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5215,17 +5231,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -5253,32 +5269,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5286,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5310,17 +5330,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5330,17 +5350,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -5368,32 +5388,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5401,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5425,33 +5449,37 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB42" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -5479,32 +5507,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5512,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5536,17 +5568,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5556,17 +5588,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5666,7 +5698,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5709,32 +5741,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5742,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5766,17 +5802,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5786,17 +5822,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5976,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6030,7 +6066,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6145,7 +6181,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6260,7 +6296,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -6321,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6375,7 +6411,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -6436,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6551,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6666,7 +6702,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6777,7 +6813,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6892,7 +6928,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6946,7 +6982,685 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>9/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A92076D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr"/>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>134.5</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>16/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr"/>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>9/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr"/>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>17/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-17-浦东35路.xlsx
+++ b/data/export/2026-10-17-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC61"/>
+  <dimension ref="A1:AC67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2617,17 +2617,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,12 +2969,12 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3207,14 +3207,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>130.0</t>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3450,17 +3450,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3683,17 +3683,17 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4638,7 +4638,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4757,7 +4757,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5626,32 +5626,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5659,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5683,17 +5687,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5703,17 +5707,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5897,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5979,32 +5983,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -6012,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6036,27 +6044,27 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
@@ -6094,32 +6102,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -6127,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6151,29 +6163,29 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
           <t>130.0</t>
@@ -6181,7 +6193,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -6209,32 +6221,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -6242,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6266,17 +6282,17 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
@@ -6286,17 +6302,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -6324,32 +6340,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6357,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6381,32 +6401,32 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6472,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6511,7 +6531,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6526,7 +6546,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6702,7 +6722,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6741,7 +6761,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6813,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6928,7 +6948,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6982,7 +7002,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -7043,7 +7063,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7154,7 +7174,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7208,7 +7228,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -7269,7 +7289,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7380,7 +7400,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7434,7 +7454,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -7495,7 +7515,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7606,7 +7626,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7650,17 +7670,703 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>20/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>8/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>22/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>130.5</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>12/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>144.5</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>24/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-17-浦东35路.xlsx
+++ b/data/export/2026-10-17-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC67"/>
+  <dimension ref="A1:AC68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3807,17 +3807,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4638,7 +4638,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -6312,7 +6312,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6459,32 +6459,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6492,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6516,17 +6520,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6536,17 +6540,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6722,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6833,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6948,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7002,7 +7006,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -7063,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7174,7 +7178,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7289,7 +7293,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7400,7 +7404,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7454,7 +7458,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -7515,7 +7519,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7626,7 +7630,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7741,7 +7745,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7856,7 +7860,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7910,7 +7914,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -7971,7 +7975,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8086,7 +8090,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8130,17 +8134,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -8201,7 +8205,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8263,22 +8267,22 @@
       <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -8316,7 +8320,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8330,41 +8334,156 @@
       <c r="T67" s="2" t="inlineStr"/>
       <c r="U67" s="2" t="inlineStr">
         <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>23/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
           <t>14:35</t>
         </is>
       </c>
-      <c r="V67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W67" s="2" t="inlineStr">
+      <c r="W68" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X67" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y67" s="2" t="inlineStr">
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z67" s="2" t="inlineStr">
+      <c r="Z68" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
+      <c r="AA68" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB67" s="2" t="inlineStr"/>
-      <c r="AC67" s="2" t="inlineStr">
+      <c r="AB68" s="2" t="inlineStr"/>
+      <c r="AC68" s="2" t="inlineStr">
         <is>
           <t>—/28</t>
         </is>

--- a/data/export/2026-10-17-浦东35路.xlsx
+++ b/data/export/2026-10-17-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC68"/>
+  <dimension ref="A1:AC72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,14 +827,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>126.5</t>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,13 +1185,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,14 +1299,14 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
           <t>129.5</t>
@@ -1310,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1529,22 +1533,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1653,12 +1657,12 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1782,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,18 +2021,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2143,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2454,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2508,7 +2516,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2930,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2984,7 +2992,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3111,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3222,7 +3230,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3341,7 +3349,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3698,7 +3706,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>26/28</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3771,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3817,7 +3825,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3890,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3921,14 +3929,14 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
           <t>126.5</t>
@@ -3936,7 +3944,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4009,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4045,7 +4053,7 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
@@ -4170,7 +4178,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4275,13 +4283,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB32" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4465,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4504,14 +4516,14 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
           <t>129.5</t>
@@ -4519,7 +4531,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4623,22 +4635,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -4757,7 +4769,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4949,7 +4961,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4993,12 +5005,12 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5241,7 +5253,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -5360,7 +5372,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5437,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5479,7 +5491,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5556,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5598,7 +5610,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5675,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -6020,7 +6032,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6074,7 +6086,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6151,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6193,7 +6205,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6389,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6431,7 +6443,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>26/28</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6508,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6550,7 +6562,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -6578,32 +6590,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -6611,7 +6627,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6635,17 +6651,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6655,7 +6671,7 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
@@ -6693,32 +6709,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6726,7 +6746,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6750,17 +6770,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6770,13 +6790,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB53" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6861,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6919,32 +6943,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -6952,7 +6980,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6976,37 +7004,37 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7062,12 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq37推进至seq51，推进14站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -7067,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7075,10 +7103,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q56" s="2" t="inlineStr"/>
-      <c r="R56" s="2" t="inlineStr"/>
-      <c r="S56" s="2" t="inlineStr"/>
-      <c r="T56" s="2" t="inlineStr"/>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置浦建路锦绣路 ETA 9分钟参与校验</t>
+        </is>
+      </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
           <t>12:28</t>
@@ -7145,32 +7189,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -7178,7 +7226,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7202,17 +7250,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7222,12 +7270,12 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7260,32 +7308,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7293,7 +7345,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7317,33 +7369,37 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB58" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -7404,7 +7460,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7458,7 +7514,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -7519,7 +7575,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7630,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7745,7 +7801,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7799,7 +7855,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7916,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7914,7 +7970,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -7975,7 +8031,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8029,7 +8085,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -8090,7 +8146,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8144,7 +8200,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -8205,7 +8261,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8259,7 +8315,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>26/28</t>
         </is>
       </c>
     </row>
@@ -8320,7 +8376,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8374,7 +8430,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -8435,7 +8491,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8479,13 +8535,477 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB68" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>126.5</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>137.5</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>20/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>129.5</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>9/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>23/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-17-浦东35路.xlsx
+++ b/data/export/2026-10-17-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC72"/>
+  <dimension ref="A1:AC77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>26/28</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2391,13 +2391,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>27/28</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2506,17 +2510,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2625,17 +2629,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2758,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3057,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3096,7 +3100,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3176,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3220,17 +3224,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3299,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3349,7 +3353,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3537,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3572,14 +3576,14 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>132.0</t>
@@ -3587,7 +3591,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3656,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3706,7 +3710,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>26/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -3771,7 +3775,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3890,7 +3894,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4239,7 +4243,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4477,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4596,7 +4600,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4645,12 +4649,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4885,7 +4889,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4961,7 +4965,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5010,7 +5014,7 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5080,7 +5084,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5119,7 +5123,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5318,7 +5322,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5357,7 +5361,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5437,7 +5441,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5556,7 +5560,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5600,17 +5604,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -5675,7 +5679,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5719,17 +5723,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -5848,7 +5852,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -6032,7 +6036,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6151,7 +6155,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6195,17 +6199,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -6389,7 +6393,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6443,7 +6447,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>26/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -6508,7 +6512,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6746,7 +6750,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6953,24 +6957,24 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6980,7 +6984,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7029,12 +7033,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -7067,7 +7071,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq37推进至seq51，推进14站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq37推进至seq63，推进26站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -7095,7 +7099,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7150,7 +7154,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7199,24 +7203,24 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -7226,7 +7230,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7275,7 +7279,7 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7318,24 +7322,24 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7345,7 +7349,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7394,12 +7398,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>26/28</t>
         </is>
       </c>
     </row>
@@ -7460,7 +7464,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7542,32 +7546,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -7575,7 +7583,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7599,17 +7607,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7619,13 +7627,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB60" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>27/28</t>
         </is>
       </c>
     </row>
@@ -7653,32 +7665,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -7686,7 +7702,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7710,17 +7726,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7730,17 +7746,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -7768,32 +7784,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -7801,7 +7821,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7825,17 +7845,17 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7845,17 +7865,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -7883,32 +7903,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -7916,7 +7940,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7940,17 +7964,17 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -7960,17 +7984,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8055,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8146,7 +8170,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8261,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8315,7 +8339,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>26/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -8376,7 +8400,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8430,7 +8454,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8515,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8606,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8721,7 +8745,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8770,12 +8794,12 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -8836,7 +8860,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8898,22 +8922,22 @@
       <c r="A72" s="2" t="inlineStr"/>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A92076D</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -8946,12 +8970,12 @@
       <c r="M72" s="2" t="inlineStr"/>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8965,47 +8989,618 @@
       <c r="T72" s="2" t="inlineStr"/>
       <c r="U72" s="2" t="inlineStr">
         <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
           <t>15:25</t>
         </is>
       </c>
-      <c r="V72" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W72" s="2" t="inlineStr">
+      <c r="W73" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X72" s="2" t="inlineStr">
+      <c r="X73" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y72" s="2" t="inlineStr">
+      <c r="Y73" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z72" s="2" t="inlineStr">
+      <c r="Z73" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
+      <c r="AA73" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB72" s="2" t="inlineStr">
-        <is>
-          <t>141.0</t>
-        </is>
-      </c>
-      <c r="AC72" s="2" t="inlineStr">
-        <is>
-          <t>23/28</t>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>26/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>18/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>15/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>128.5</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>6/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-17-浦东35路.xlsx
+++ b/data/export/2026-10-17-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC77"/>
+  <dimension ref="A1:AC84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2986,17 +2986,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3343,17 +3343,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4287,17 +4287,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5837,7 +5837,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6080,17 +6080,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -6155,7 +6155,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6274,7 +6274,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6556,12 +6556,12 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6750,7 +6750,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6794,17 +6794,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -6984,7 +6984,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7038,7 +7038,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7556,24 +7556,24 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>149分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7583,7 +7583,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7622,7 +7622,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7632,7 +7632,7 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7794,24 +7794,24 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -7913,12 +7913,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7989,7 +7989,7 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8022,32 +8022,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -8055,7 +8059,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8079,17 +8083,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8099,17 +8103,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -8137,32 +8141,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8170,7 +8178,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8194,17 +8202,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8214,12 +8222,12 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8252,32 +8260,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8285,7 +8297,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8309,17 +8321,17 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8329,12 +8341,12 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8367,32 +8379,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8400,7 +8416,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8424,17 +8440,17 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8444,17 +8460,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -8482,32 +8498,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8515,7 +8535,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8539,17 +8559,17 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
@@ -8559,17 +8579,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8650,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8684,7 +8704,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -8745,7 +8765,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8799,7 +8819,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -8860,7 +8880,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8914,7 +8934,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8995,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9086,7 +9106,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9201,7 +9221,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9316,7 +9336,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9431,7 +9451,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9546,7 +9566,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9604,6 +9624,811 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>27/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>15/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>130.5</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>13/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>19/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>22/28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-17-浦东35路.xlsx
+++ b/data/export/2026-10-17-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC84"/>
+  <dimension ref="A1:AC90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,22 +1299,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1538,17 +1538,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1652,14 +1652,14 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
           <t>134.3</t>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
           <t>130.0</t>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3338,22 +3338,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3933,22 +3933,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4520,22 +4520,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4644,17 +4644,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5004,14 +5004,14 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
           <t>134.3</t>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -5679,7 +5679,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5718,14 +5718,14 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
           <t>130.0</t>
@@ -5733,7 +5733,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5852,7 +5852,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -6090,7 +6090,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -6750,7 +6750,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -6984,7 +6984,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7028,17 +7028,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7269,14 +7269,14 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
           <t>134.3</t>
@@ -7284,7 +7284,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -7349,7 +7349,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7741,14 +7741,14 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
           <t>130.0</t>
@@ -7756,7 +7756,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -7994,7 +7994,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -8113,7 +8113,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -8232,7 +8232,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -8270,24 +8270,24 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -8297,7 +8297,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8389,24 +8389,24 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8455,22 +8455,22 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -8508,24 +8508,24 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8584,12 +8584,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -8617,32 +8617,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8650,7 +8654,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8674,37 +8678,37 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA69" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -8732,32 +8736,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -8765,7 +8773,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8789,17 +8797,17 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
@@ -8809,17 +8817,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -8847,32 +8855,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8880,7 +8892,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8904,37 +8916,37 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -8962,12 +8974,12 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq38推进至seq58，推进20站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -8995,7 +9007,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9003,10 +9015,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q72" s="2" t="inlineStr"/>
-      <c r="R72" s="2" t="inlineStr"/>
-      <c r="S72" s="2" t="inlineStr"/>
-      <c r="T72" s="2" t="inlineStr"/>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>物理seq22（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="S72" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="T72" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq22映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±6分钟；反向位置物理seq38（站名待映射） ETA 7分钟参与校验</t>
+        </is>
+      </c>
       <c r="U72" s="2" t="inlineStr">
         <is>
           <t>15:22</t>
@@ -9106,7 +9134,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9221,7 +9249,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9336,7 +9364,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9390,7 +9418,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -9451,7 +9479,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9505,7 +9533,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -9566,7 +9594,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9620,7 +9648,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9709,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9796,7 +9824,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9850,7 +9878,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9939,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10026,7 +10054,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10080,7 +10108,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -10141,7 +10169,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10195,7 +10223,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10284,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10310,7 +10338,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -10371,7 +10399,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10429,6 +10457,696 @@
         </is>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>134.3</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>16/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>24/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>8/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>134.3</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>16/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>8/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>133.3</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>15/28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-17-浦东35路.xlsx
+++ b/data/export/2026-10-17-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC90"/>
+  <dimension ref="A1:AC99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,22 +1890,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2021,22 +2021,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>26/28</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2260,17 +2260,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2391,17 +2391,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>27/28</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2748,17 +2748,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2862,14 +2862,14 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
           <t>73.5</t>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3100,22 +3100,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3219,14 +3219,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>131.0</t>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3576,22 +3576,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4900,7 +4900,7 @@
       <c r="AB37" s="2" t="inlineStr"/>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5123,22 +5123,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5257,7 +5257,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5366,17 +5366,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -5614,7 +5614,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -5679,7 +5679,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5842,17 +5842,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5956,14 +5956,14 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
           <t>73.5</t>
@@ -5971,7 +5971,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -6090,7 +6090,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -6155,7 +6155,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6194,14 +6194,14 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
           <t>131.0</t>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -6919,7 +6919,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7165,7 +7165,7 @@
       <c r="AB56" s="2" t="inlineStr"/>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -7230,7 +7230,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -7349,7 +7349,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7388,22 +7388,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>26/28</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7627,17 +7627,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>27/28</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7756,7 +7756,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -7875,7 +7875,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7979,14 +7979,14 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
           <t>131.0</t>
@@ -7994,7 +7994,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -8113,7 +8113,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -8232,7 +8232,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -8351,7 +8351,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8470,7 +8470,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -8589,7 +8589,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -8654,7 +8654,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8708,7 +8708,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -8827,7 +8827,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -8892,7 +8892,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8946,7 +8946,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -9007,7 +9007,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -9073,7 +9073,7 @@
       <c r="AB72" s="2" t="inlineStr"/>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -9101,32 +9101,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -9134,7 +9138,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9158,37 +9162,37 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>26/28</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -9216,32 +9220,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -9249,7 +9257,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9273,37 +9281,37 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA74" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -9331,32 +9339,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9364,7 +9376,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9388,37 +9400,37 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -9446,32 +9458,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9479,7 +9495,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9503,37 +9519,37 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA76" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -9561,32 +9577,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9594,7 +9614,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9618,17 +9638,17 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
@@ -9638,17 +9658,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -9676,32 +9696,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9709,7 +9733,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9733,17 +9757,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9753,17 +9777,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>27/28</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -9791,32 +9815,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -9824,7 +9852,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9848,17 +9876,17 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
@@ -9868,17 +9896,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -9939,7 +9967,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9993,7 +10021,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -10054,7 +10082,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10093,7 +10121,7 @@
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
@@ -10108,7 +10136,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -10169,7 +10197,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10223,7 +10251,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -10284,7 +10312,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10338,7 +10366,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -10399,7 +10427,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10453,7 +10481,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -10514,7 +10542,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10568,7 +10596,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -10629,7 +10657,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10683,7 +10711,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10772,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10798,7 +10826,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -10859,7 +10887,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10913,7 +10941,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -10974,7 +11002,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11028,7 +11056,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -11089,7 +11117,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11143,7 +11171,1034 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>12/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>150.5</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>27/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A92076D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr"/>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>73.5</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>10/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr"/>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>13/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>136.7</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>19/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>130.5</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>16/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-17-浦东35路.xlsx
+++ b/data/export/2026-10-17-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC99"/>
+  <dimension ref="A1:AC100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3462,17 +3462,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4172,17 +4172,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5679,7 +5679,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6155,7 +6155,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6318,17 +6318,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -7349,7 +7349,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7622,7 +7622,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7632,7 +7632,7 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7756,7 +7756,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -8232,7 +8232,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8654,7 +8654,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8708,7 +8708,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -8892,7 +8892,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8946,7 +8946,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -9007,7 +9007,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9430,7 +9430,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9668,7 +9668,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -9706,12 +9706,12 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>147分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9772,7 +9772,7 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9782,7 +9782,7 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9934,32 +9934,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9967,7 +9971,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9991,17 +9995,17 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
@@ -10011,17 +10015,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -10049,32 +10053,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10082,7 +10090,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10106,17 +10114,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10126,17 +10134,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -10197,7 +10205,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10251,7 +10259,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -10312,7 +10320,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10427,7 +10435,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10542,7 +10550,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10596,7 +10604,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -10657,7 +10665,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10772,7 +10780,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10826,7 +10834,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -10887,7 +10895,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10941,7 +10949,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -11002,7 +11010,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11056,7 +11064,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -11117,7 +11125,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11171,7 +11179,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -11232,7 +11240,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11347,7 +11355,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11458,7 +11466,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11573,7 +11581,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11627,7 +11635,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -11688,7 +11696,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11799,7 +11807,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11853,7 +11861,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -11914,7 +11922,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12029,7 +12037,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12073,17 +12081,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -12144,7 +12152,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12202,6 +12210,121 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>26/29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-17-浦东35路.xlsx
+++ b/data/export/2026-10-17-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC100"/>
+  <dimension ref="A1:AC105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1776,17 +1776,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3343,17 +3343,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4052,22 +4052,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5247,17 +5247,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -5679,7 +5679,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5837,7 +5837,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6090,7 +6090,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -6155,7 +6155,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6274,7 +6274,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6670,22 +6670,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7583,7 +7583,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7632,7 +7632,7 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8460,17 +8460,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -8654,7 +8654,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8892,7 +8892,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9495,7 +9495,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9614,7 +9614,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9706,24 +9706,24 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9733,7 +9733,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9782,7 +9782,7 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -9956,12 +9956,12 @@
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9971,7 +9971,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -10063,24 +10063,24 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -10090,7 +10090,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10205,7 +10205,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
@@ -10287,32 +10287,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -10320,7 +10324,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10344,37 +10348,37 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA83" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -10402,32 +10406,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10435,7 +10443,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10459,17 +10467,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10479,17 +10487,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -10550,7 +10558,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10632,32 +10640,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10665,7 +10677,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10689,17 +10701,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10709,17 +10721,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -10780,7 +10792,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10895,7 +10907,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -11010,7 +11022,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11125,7 +11137,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11240,7 +11252,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11355,7 +11367,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11466,7 +11478,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11581,7 +11593,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11696,7 +11708,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11807,7 +11819,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11922,7 +11934,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12037,7 +12049,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12086,7 +12098,7 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
@@ -12152,7 +12164,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12214,22 +12226,22 @@
       <c r="A100" s="2" t="inlineStr"/>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -12262,12 +12274,12 @@
       <c r="M100" s="2" t="inlineStr"/>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12281,47 +12293,622 @@
       <c r="T100" s="2" t="inlineStr"/>
       <c r="U100" s="2" t="inlineStr">
         <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>8/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="V100" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W100" s="2" t="inlineStr">
+      <c r="W101" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X100" s="2" t="inlineStr">
+      <c r="X101" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y100" s="2" t="inlineStr">
+      <c r="Y101" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z100" s="2" t="inlineStr">
+      <c r="Z101" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA100" s="2" t="inlineStr">
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>23/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB100" s="2" t="inlineStr">
-        <is>
-          <t>149.0</t>
-        </is>
-      </c>
-      <c r="AC100" s="2" t="inlineStr">
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
         <is>
           <t>26/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>15/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>136.3</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>17/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>4/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-17-浦东35路.xlsx
+++ b/data/export/2026-10-17-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC105"/>
+  <dimension ref="A1:AC108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1304,17 +1304,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1657,17 +1657,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2629,17 +2629,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3105,17 +3105,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3348,12 +3348,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3938,17 +3938,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4525,17 +4525,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5009,17 +5009,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5485,17 +5485,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -5679,7 +5679,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5852,7 +5852,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6155,7 +6155,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6199,7 +6199,7 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -7038,7 +7038,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7274,17 +7274,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -7349,7 +7349,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7508,17 +7508,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7746,17 +7746,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8098,7 +8098,7 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8465,12 +8465,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -8654,7 +8654,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8698,17 +8698,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -8827,7 +8827,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -8892,7 +8892,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8936,17 +8936,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -9007,7 +9007,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9311,7 +9311,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -9376,7 +9376,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9420,17 +9420,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9668,7 +9668,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -9971,7 +9971,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10025,7 +10025,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -10090,7 +10090,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10144,7 +10144,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10324,7 +10324,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10482,7 +10482,7 @@
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr">
@@ -10525,32 +10525,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:46</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -10558,7 +10562,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10582,17 +10586,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10602,17 +10606,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -10650,24 +10654,24 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -10677,7 +10681,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10726,12 +10730,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -10759,32 +10763,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -10792,7 +10800,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10816,17 +10824,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10836,17 +10844,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -10874,32 +10882,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10907,7 +10919,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10931,17 +10943,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10951,17 +10963,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -10989,32 +11001,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:08</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -11022,7 +11038,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11046,17 +11062,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11066,17 +11082,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -11104,32 +11120,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11137,7 +11157,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11161,17 +11181,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11181,17 +11201,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -11252,7 +11272,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11334,12 +11354,12 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq37推进至seq58，推进21站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -11367,7 +11387,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11375,10 +11395,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q92" s="2" t="inlineStr"/>
-      <c r="R92" s="2" t="inlineStr"/>
-      <c r="S92" s="2" t="inlineStr"/>
-      <c r="T92" s="2" t="inlineStr"/>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
+      <c r="S92" s="2" t="inlineStr">
+        <is>
+          <t>19:16</t>
+        </is>
+      </c>
+      <c r="T92" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置浦建路锦绣路 ETA 9分钟参与校验</t>
+        </is>
+      </c>
       <c r="U92" s="2" t="inlineStr">
         <is>
           <t>18:12</t>
@@ -11478,7 +11514,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11517,7 +11553,7 @@
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
@@ -11560,32 +11596,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:36</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -11593,7 +11633,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11617,17 +11657,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11637,7 +11677,7 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
@@ -11647,7 +11687,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -11708,7 +11748,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11786,32 +11826,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11819,7 +11863,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11843,17 +11887,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11863,17 +11907,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11978,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11988,7 +12032,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -12049,7 +12093,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12103,7 +12147,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -12164,7 +12208,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12218,7 +12262,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -12279,7 +12323,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12333,7 +12377,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -12394,7 +12438,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12509,7 +12553,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12624,7 +12668,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12678,7 +12722,7 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -12739,7 +12783,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12793,7 +12837,7 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -12801,22 +12845,22 @@
       <c r="A105" s="2" t="inlineStr"/>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>20:05</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
@@ -12849,12 +12893,12 @@
       <c r="M105" s="2" t="inlineStr"/>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12868,47 +12912,392 @@
       <c r="T105" s="2" t="inlineStr"/>
       <c r="U105" s="2" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>140.7</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>24/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
           <t>20:05</t>
         </is>
       </c>
-      <c r="V105" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W105" s="2" t="inlineStr">
+      <c r="W106" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X105" s="2" t="inlineStr">
+      <c r="X106" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y105" s="2" t="inlineStr">
+      <c r="Y106" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z105" s="2" t="inlineStr">
+      <c r="Z106" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA105" s="2" t="inlineStr">
+      <c r="AA106" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB105" s="2" t="inlineStr">
+      <c r="AB106" s="2" t="inlineStr">
         <is>
           <t>129.0</t>
         </is>
       </c>
-      <c r="AC105" s="2" t="inlineStr">
+      <c r="AC106" s="2" t="inlineStr">
         <is>
           <t>4/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr"/>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr"/>
+      <c r="R107" s="2" t="inlineStr"/>
+      <c r="S107" s="2" t="inlineStr"/>
+      <c r="T107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W107" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z107" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA107" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB107" s="2" t="inlineStr">
+        <is>
+          <t>138.7</t>
+        </is>
+      </c>
+      <c r="AC107" s="2" t="inlineStr">
+        <is>
+          <t>20/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr"/>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr"/>
+      <c r="R108" s="2" t="inlineStr"/>
+      <c r="S108" s="2" t="inlineStr"/>
+      <c r="T108" s="2" t="inlineStr"/>
+      <c r="U108" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V108" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W108" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y108" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z108" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA108" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB108" s="2" t="inlineStr">
+        <is>
+          <t>73.5</t>
+        </is>
+      </c>
+      <c r="AC108" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-17-浦东35路.xlsx
+++ b/data/export/2026-10-17-浦东35路.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1895,17 +1895,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>28/29</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3229,12 +3229,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3581,17 +3581,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -3948,7 +3948,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5852,7 +5852,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6090,7 +6090,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -6155,7 +6155,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -7403,7 +7403,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>28/29</t>
         </is>
       </c>
     </row>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7989,12 +7989,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -8351,7 +8351,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -8470,7 +8470,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -8708,7 +8708,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -8827,7 +8827,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -9192,7 +9192,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>28/29</t>
         </is>
       </c>
     </row>
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9301,17 +9301,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -9376,7 +9376,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9495,7 +9495,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9539,17 +9539,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9658,12 +9658,12 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9733,7 +9733,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9787,7 +9787,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -9852,7 +9852,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -9971,7 +9971,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10025,7 +10025,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -10090,7 +10090,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10205,7 +10205,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10324,7 +10324,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -10443,7 +10443,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10735,7 +10735,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -10854,7 +10854,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -10973,7 +10973,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -11326,7 +11326,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>28/29</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11606,24 +11606,24 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>20:36</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -11633,7 +11633,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11682,12 +11682,12 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -11715,32 +11715,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>17:51</t>
@@ -11748,7 +11752,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11772,17 +11776,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11792,13 +11796,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB95" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -11848,12 +11856,12 @@
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -11863,7 +11871,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11945,32 +11953,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -11978,7 +11990,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12002,17 +12014,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -12022,17 +12034,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -12060,12 +12072,12 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq59，推进31站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -12093,7 +12105,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12101,10 +12113,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q98" s="2" t="inlineStr"/>
-      <c r="R98" s="2" t="inlineStr"/>
-      <c r="S98" s="2" t="inlineStr"/>
-      <c r="T98" s="2" t="inlineStr"/>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>物理seq27（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr">
+        <is>
+          <t>20:03</t>
+        </is>
+      </c>
+      <c r="S98" s="2" t="inlineStr">
+        <is>
+          <t>20:12</t>
+        </is>
+      </c>
+      <c r="T98" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U98" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -12175,32 +12203,36 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12208,7 +12240,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12232,17 +12264,17 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
@@ -12252,17 +12284,17 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -12290,32 +12322,36 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:29</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -12323,7 +12359,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12347,17 +12383,17 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
@@ -12367,12 +12403,12 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
@@ -12405,12 +12441,12 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq28推进至seq52，推进24站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -12438,7 +12474,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12446,10 +12482,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q101" s="2" t="inlineStr"/>
-      <c r="R101" s="2" t="inlineStr"/>
-      <c r="S101" s="2" t="inlineStr"/>
-      <c r="T101" s="2" t="inlineStr"/>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>物理seq30（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R101" s="2" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
+      <c r="S101" s="2" t="inlineStr">
+        <is>
+          <t>20:33</t>
+        </is>
+      </c>
+      <c r="T101" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq30映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq28（站名待映射） ETA 1分钟参与校验</t>
+        </is>
+      </c>
       <c r="U101" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -12492,7 +12544,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -12553,7 +12605,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12607,7 +12659,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -12668,7 +12720,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12722,7 +12774,7 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -12783,7 +12835,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12837,7 +12889,7 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -12898,7 +12950,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12952,7 +13004,7 @@
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -13013,7 +13065,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13128,7 +13180,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13243,7 +13295,7 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">

--- a/data/export/2026-10-17-浦东35路.xlsx
+++ b/data/export/2026-10-17-浦东35路.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2748,17 +2748,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3948,7 +3948,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4172,17 +4172,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5842,17 +5842,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5961,12 +5961,12 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -7038,7 +7038,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8708,7 +8708,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -8827,7 +8827,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -8946,7 +8946,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -9549,7 +9549,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -9852,7 +9852,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9896,17 +9896,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -9971,7 +9971,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10015,17 +10015,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10324,7 +10324,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10973,7 +10973,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
@@ -12044,7 +12044,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -12294,7 +12294,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -12446,7 +12446,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq28推进至seq52，推进24站，达到≥2站确认条件</t>
+          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12687,32 +12687,36 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:46</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12720,7 +12724,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12744,17 +12748,17 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z103" s="2" t="inlineStr">
@@ -12764,17 +12768,17 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -12802,32 +12806,36 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:47</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M104" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -12835,7 +12843,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12859,17 +12867,17 @@
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y104" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z104" s="2" t="inlineStr">
@@ -12879,17 +12887,17 @@
       </c>
       <c r="AA104" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -12950,7 +12958,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -13065,7 +13073,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13180,7 +13188,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13262,32 +13270,36 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:53</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>58分钟</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M108" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -13295,7 +13307,7 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
@@ -13319,17 +13331,17 @@
       </c>
       <c r="W108" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X108" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y108" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z108" s="2" t="inlineStr">
@@ -13339,12 +13351,12 @@
       </c>
       <c r="AA108" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB108" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="AC108" s="2" t="inlineStr">
